--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -582,11 +582,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -674,11 +674,11 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>671</v>
+        <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -766,11 +766,11 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -950,11 +950,11 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,106 +425,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_Deadline_Date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statute_Citation</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -582,31 +604,41 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -674,31 +706,41 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -766,31 +808,41 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -858,31 +910,41 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -950,31 +1012,41 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,115 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Parcel_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Record_Type</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -553,92 +568,107 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2024-TX-04812</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>WILLIAM &amp; MARY HOLLOWAY</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F2" t="b">
+      <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="b">
+      <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>128500</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>32125</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>55</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -655,92 +685,107 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2024-TX-04950</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ESTATE OF CHARLES BEAUMONT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>86200</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>21550</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>55</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -757,92 +802,107 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2024-TX-02044</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ESTATE OF MARGARET THORNTON</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>6412 ABRAMS RD DALLAS TX 75231</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>77800</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>19450</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>55</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -859,92 +919,107 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>2024-TX-01928</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>GEORGE &amp; DOROTHY WASHINGTON</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F5" t="b">
+      <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="b">
+      <c r="H5" t="b">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>3819 COLONIAL AVE DALLAS TX 75215</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>59400</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>14850</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>55</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -961,92 +1036,107 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>2024-TX-05110</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>RAFAEL GUERRERO</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F6" t="b">
+      <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="b">
+      <c r="H6" t="b">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>41300</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>10325</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>55</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18346,7 +18346,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18474,7 +18474,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18602,7 +18602,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20522,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21674,7 +21674,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22186,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22698,7 +22698,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18346,7 +18346,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18474,7 +18474,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18602,7 +18602,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20522,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21674,7 +21674,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22186,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22698,7 +22698,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18346,7 +18346,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18474,7 +18474,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18602,7 +18602,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20522,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21674,7 +21674,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22186,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22698,7 +22698,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Linda L. Robinson / Yolanda Humphrey</t>
+          <t>Karina Andrade / Yolanda Humphrey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FBC General Fund / Roy Varghese Panakezham</t>
+          <t>Roy Varghese Panakezham / Blair K Woodard</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>J.D. Whitehead / Clive L Sheppard</t>
+          <t>Charmian Strifert / Frank Lamole</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>. RAMON BASILIO PAREDES ET AL</t>
+          <t>RAMON BASILIO PAREDES ET AL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2030-08-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2110</v>
+        <v>688</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2032-07-31</t>
+          <t>2028-09-10</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Charles F Sherwood / Sam R Casey Sr</t>
+          <t>Floyd Adair / Return to sender 09 / 11 / 2026 / Catherine Elizabeth Casey</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melinda Wiggins / United States of America</t>
+          <t>Karina Andrade / Yanira Marie Reyes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Evelyn S Long / Dorothy A Handy</t>
+          <t>George Pallissard (2nd Address) (Returned to Sender) / Lucille Carroll (2nd Address) (Returned to Sender)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>. TRUDY MAITEN ET AL</t>
+          <t>TRUDY MAITEN ET AL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25-DCV-334201</t>
+          <t>24-DCV-320773</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yolanda Humphery / FBC General Fund</t>
+          <t>Alexander Freeman / Eula Webster Freeman</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>98957.25</v>
+        <v>88392.85000000001</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>24739.31</v>
+        <v>22098.21</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=25-DCV-334201</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=24-DCV-320773</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 25-DCV-334201</t>
+          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 24-DCV-320773</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1986,18 +1986,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fort Bend</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24-DCV-320773</t>
+          <t>TX-25-01403</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alexander Freeman / Eula Webster Freeman</t>
+          <t>JAMES L. DAWKINS, AKA JIM L DAWKINS TRACK 1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Fort Bend County District Court Registry, Richmond, TX</t>
+          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>88392.85000000001</v>
+        <v>78008.14999999999</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>22098.21</v>
+        <v>19502.04</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -2039,11 +2039,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>729</v>
+        <v>688</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-09-10</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2062,17 +2062,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=24-DCV-320773</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-25-01403</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 24-DCV-320773</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-25-01403</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2120,12 +2120,12 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TX-25-01403</t>
+          <t>TX-25-01003</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>. JAMES L. DAWKINS, AKA JIM L DAWKINS TRACK 1</t>
+          <t>JOSE SANCHEZ et al</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>78008.14999999999</v>
+        <v>73200.14</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>19502.04</v>
+        <v>18300.03</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -2167,11 +2167,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2030-08-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2110</v>
+        <v>688</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2032-07-31</t>
+          <t>2028-09-10</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-25-01403</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-25-01003</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-25-01403</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-25-01003</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2248,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TX-25-01003</t>
+          <t>TX-23-00379</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JOSE SANCHEZ et al</t>
+          <t>HAZEL LOUI8SE STEVERSON ETAL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>73200.14</v>
+        <v>69126.92999999999</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>18300.03</v>
+        <v>17281.73</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2295,11 +2295,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2030-08-01</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2110</v>
+        <v>691</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2032-07-31</t>
+          <t>2028-09-13</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-25-01003</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-00379</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-25-01003</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-00379</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2370,18 +2370,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Fort Bend</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TX-23-00379</t>
+          <t>16-DCV-232002</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HAZEL LOUI8SE STEVERSON ETAL</t>
+          <t>Kimyung Celina Huynh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
+          <t>Fort Bend County District Court Registry, Richmond, TX</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>69126.92999999999</v>
+        <v>67474.62</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>17281.73</v>
+        <v>16868.65</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2423,11 +2423,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2028-08-31</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1410</v>
+        <v>729</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2030-08-31</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-00379</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=16-DCV-232002</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-00379</t>
+          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 16-DCV-232002</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2498,18 +2498,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fort Bend</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16-DCV-232002</t>
+          <t>TX-23-02127</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kimyung Celina Huynh</t>
+          <t>J J LUCAS AKA JOHN LUCAS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Fort Bend County District Court Registry, Richmond, TX</t>
+          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>67474.62</v>
+        <v>66305.14999999999</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>16868.65</v>
+        <v>16576.29</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2551,11 +2551,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>729</v>
+        <v>531</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-04-06</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=16-DCV-232002</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-02127</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 16-DCV-232002</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-02127</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2632,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TX-23-02127</t>
+          <t>TX-24-00788</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>J J LUCAS AKA JOHN LUCAS</t>
+          <t>JOSE M VILLAFANA ETAL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>66305.14999999999</v>
+        <v>65211.47</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>16576.29</v>
+        <v>16302.87</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2679,11 +2679,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2028-04-06</t>
+          <t>2028-05-04</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-02127</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-24-00788</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-02127</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-24-00788</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2754,18 +2754,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Fort Bend</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TX-24-00788</t>
+          <t>19-DCV-261514</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JOSE M VILLAFANA ETAL</t>
+          <t>Guadalupe Cortez / Socorro Cortez Torres</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
+          <t>Fort Bend County District Court Registry, Richmond, TX</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>65211.47</v>
+        <v>63006.3</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>16302.87</v>
+        <v>15751.58</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2807,11 +2807,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>561</v>
+        <v>729</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2028-05-04</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-24-00788</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=19-DCV-261514</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-24-00788</t>
+          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 19-DCV-261514</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2882,18 +2882,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fort Bend</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19-DCV-261514</t>
+          <t>TX-23-01466</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jovita Cortez Martinez / Gloria Cortez Jasso</t>
+          <t>RAMIRO BAHENA et al</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Fort Bend County District Court Registry, Richmond, TX</t>
+          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>63006.3</v>
+        <v>62862.56</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>15751.58</v>
+        <v>15715.64</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2935,11 +2935,11 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>729</v>
+        <v>496</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-03-02</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=19-DCV-261514</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-01466</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 19-DCV-261514</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-01466</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TX-23-01466</t>
+          <t>TX-23-00079</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAMIRO BAHENA et al</t>
+          <t>CATHY D. CANNON</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>62862.56</v>
+        <v>62512.86</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>15715.64</v>
+        <v>15628.22</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -3063,20 +3063,20 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>498</v>
+        <v>76</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2028-03-02</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-01466</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-00079</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-01466</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-00079</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3138,18 +3138,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Fort Bend</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TX-23-00079</t>
+          <t>19-DCV-267691</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>. CATHY D. CANNON</t>
+          <t>Wendell Dean Wyatt / Tracy Lee Wyatt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
+          <t>Fort Bend County District Court Registry, Richmond, TX</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>62512.86</v>
+        <v>61695.32</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>15628.22</v>
+        <v>15423.83</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -3191,20 +3191,20 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>78</v>
+        <v>729</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3214,17 +3214,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-00079</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=19-DCV-267691</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-00079</t>
+          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 19-DCV-267691</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3266,18 +3266,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fort Bend</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19-DCV-267691</t>
+          <t>TX-22-00007</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wendell Dean Wyatt / Tracy Lee Wyatt</t>
+          <t>LAVONA COOK, A / K / A LOVAA COOK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Fort Bend County District Court Registry, Richmond, TX</t>
+          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>61695.32</v>
+        <v>60238.34</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>15423.83</v>
+        <v>15059.58</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3319,11 +3319,11 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>729</v>
+        <v>586</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-05-31</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3342,17 +3342,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=19-DCV-267691</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-22-00007</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 19-DCV-267691</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-22-00007</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3394,18 +3394,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Fort Bend</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TX-22-00007</t>
+          <t>24-DCV-318033</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>. LAVONA COOK, A/K/A LOVAA COOK</t>
+          <t>Yolanda M Humphrey / Walter Cienfuegos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
+          <t>Fort Bend County District Court Registry, Richmond, TX</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>60238.34</v>
+        <v>58474.13</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>15059.58</v>
+        <v>14618.53</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -3447,11 +3447,11 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>588</v>
+        <v>729</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2028-05-31</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3470,17 +3470,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-22-00007</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=24-DCV-318033</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-22-00007</t>
+          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 24-DCV-318033</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3522,18 +3522,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fort Bend</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24-DCV-318033</t>
+          <t>TX-22-00643</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yolanda M Humphrey / Jennifer C Chiang</t>
+          <t>NOBLE MAYE,A / K / A NOLEN MAYE A / K / A NOLEN MAY ET AL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Fort Bend County District Court Registry, Richmond, TX</t>
+          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>58474.13</v>
+        <v>54578.15</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>14618.53</v>
+        <v>13644.54</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3575,11 +3575,11 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>729</v>
+        <v>405</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2027-12-02</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3598,17 +3598,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=24-DCV-318033</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-22-00643</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 24-DCV-318033</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-22-00643</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3650,18 +3650,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Fort Bend</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TX-22-00643</t>
+          <t>19-DCV-263899</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NOBLE MAYE,A/K/A NOLEN MAYE A/K/A NOLEN MAY ET AL</t>
+          <t>Raymond Pope / Aaron Eugene Pope</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
+          <t>Fort Bend County District Court Registry, Richmond, TX</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>54578.15</v>
+        <v>54456.32</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>13644.54</v>
+        <v>13614.08</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3703,11 +3703,11 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>407</v>
+        <v>729</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-12-02</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-22-00643</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=19-DCV-263899</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-22-00643</t>
+          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 19-DCV-263899</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3778,18 +3778,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fort Bend</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19-DCV-263899</t>
+          <t>TX-23-01487</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raymond Pope / Aaron Eugene Pope</t>
+          <t>BOBBY R CANTRELL ET AL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Fort Bend County District Court Registry, Richmond, TX</t>
+          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>54456.32</v>
+        <v>54345.43</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>13614.08</v>
+        <v>13586.36</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3831,11 +3831,11 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>729</v>
+        <v>496</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-03-02</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3854,17 +3854,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=19-DCV-263899</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-01487</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 19-DCV-263899</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-01487</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TX-23-01487</t>
+          <t>TX-25-01403</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>. BOBBY R CANTRELL ET AL</t>
+          <t>JAMES L. DAWKINS, AKA JIM L DAWKINS TRACK 2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>54345.43</v>
+        <v>52490.12</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>13586.36</v>
+        <v>13122.53</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3959,11 +3959,11 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>498</v>
+        <v>688</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2028-03-02</t>
+          <t>2028-09-10</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-01487</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-25-01403</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-01487</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-25-01403</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4034,18 +4034,18 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Fort Bend</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TX-25-01403</t>
+          <t>21-DCV-289180</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>. JAMES L. DAWKINS, AKA JIM L DAWKINS TRACK 2</t>
+          <t>George Kemp / Prisilla Kemp</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
+          <t>Fort Bend County District Court Registry, Richmond, TX</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>52490.12</v>
+        <v>51605.73</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>13122.53</v>
+        <v>12901.43</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -4087,11 +4087,11 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2030-08-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2110</v>
+        <v>729</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2032-07-31</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4110,17 +4110,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-25-01403</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=21-DCV-289180</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-25-01403</t>
+          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 21-DCV-289180</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4162,18 +4162,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fort Bend</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21-DCV-289180</t>
+          <t>TX-24-00554</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FBC / George Kemp</t>
+          <t>ARTURO D VERA ET AL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Fort Bend County District Court Registry, Richmond, TX</t>
+          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>51605.73</v>
+        <v>50832.78</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>12901.43</v>
+        <v>12708.19</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -4215,11 +4215,11 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>729</v>
+        <v>559</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-05-04</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4238,17 +4238,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=21-DCV-289180</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-24-00554</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 21-DCV-289180</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-24-00554</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4296,12 +4296,12 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TX-24-00554</t>
+          <t>TX-22-01500</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>. ARTURO D VERA ET AL</t>
+          <t>RAMONA LARA AKA RAMONA L RAMIREZ ETAL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>50832.78</v>
+        <v>47045.39</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>12708.19</v>
+        <v>11761.35</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -4343,20 +4343,20 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>561</v>
+        <v>76</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2028-05-04</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-24-00554</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-22-01500</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-24-00554</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-22-01500</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TX-22-01500</t>
+          <t>TX-23-00804</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAMONA LARA AKA RAMONA L RAMIREZ ETAL</t>
+          <t>LEE ANDER SMITH ETAL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>47045.39</v>
+        <v>46926.42</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>11761.35</v>
+        <v>11731.6</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -4471,20 +4471,20 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-22-01500</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-00804</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-22-01500</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-00804</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4552,12 +4552,12 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TX-23-00804</t>
+          <t>TX-12-50070</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LEE ANDER SMITH ETAL</t>
+          <t>CLYDIE MAE LEE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>46926.42</v>
+        <v>46873.52</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>11731.6</v>
+        <v>11718.38</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -4599,20 +4599,20 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>43</v>
+        <v>335</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2027-09-23</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-23-00804</t>
+          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-12-50070</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-23-00804</t>
+          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-12-50070</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4674,18 +4674,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Fort Bend</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TX-12-50070</t>
+          <t>23-DCV-310277</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CLYDIE MAE LEE</t>
+          <t>Albertha Collier Davis</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Dallas County Tax Foreclosure Registry, Dallas, TX</t>
+          <t>Fort Bend County District Court Registry, Richmond, TX</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>46873.52</v>
+        <v>45983.64</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>11718.38</v>
+        <v>11495.91</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -4727,11 +4727,11 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>337</v>
+        <v>729</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2027-09-23</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4750,17 +4750,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf#search=TX-12-50070</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=23-DCV-310277</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Listed on Dallas County District Clerk Current Excess Funds PDF — Case TX-12-50070</t>
+          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 23-DCV-310277</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/Assets/uploads/docs/district-clerk/excess-funds/ExcessFunds-100126.pdf</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4808,12 +4808,12 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>23-DCV-310277</t>
+          <t>21-DCV-285387</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Albertha Collier Davis</t>
+          <t>Mark Steven Meredith / Linbarger Goggan Blair &amp; Sampson LLP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>45983.64</v>
+        <v>45744.44</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>11495.91</v>
+        <v>11436.11</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=23-DCV-310277</t>
+          <t>https://odysseyreport.fortbendcountytx.gov/District_Clerk/DC-Eligible-Unclaimed-Excess-Proceeds.pdf#search=21-DCV-285387</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 23-DCV-310277</t>
+          <t>Listed on Fort Bend County District Clerk Excess Proceeds PDF — Case 21-DCV-285387</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>. CHRIYSTAL WHITNEY ET AL</t>
+          <t>CHRIYSTAL WHITNEY ET AL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>. OBRIANT WEBB ET AL</t>
+          <t>OBRIANT WEBB ET AL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>. RUBEN LARA, JR ET AL</t>
+          <t>RUBEN LARA, JR ET AL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6007,11 +6007,11 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2028-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1410</v>
+        <v>692</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2030-08-31</t>
+          <t>2028-09-14</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>. MARY LEE CLARK GANN</t>
+          <t>MARY LEE CLARK GANN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>. JOHN COLQUITT WEST et al</t>
+          <t>JOHN COLQUITT WEST et al</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Charles Miller / Rosalie Ravkind, AKA Rosalie Mandell Ravkind</t>
+          <t>Rosalie Ravkind, AKA Rosalie Mandell Ravkind / Charles Miller</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>. JOE W. HEMPHILL ET AL</t>
+          <t>JOE W. HEMPHILL ET AL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>J.H. VELA,A/K/A JESSE H. VELA ET AL</t>
+          <t>J.H. VELA,A / K / A JESSE H. VELA ET AL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>. TOM BROWN ET AL</t>
+          <t>TOM BROWN ET AL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Daniel Valencia / Isa Valencia</t>
+          <t>Isa Valencia / Daniel Valencia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>. AREON WILSON</t>
+          <t>AREON WILSON</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>. VICTOR D HUDSON ET AL</t>
+          <t>VICTOR D HUDSON ET AL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>. MIKE JIMENEZ, AKA MIGUEL M. JIMENEZ</t>
+          <t>MIKE JIMENEZ, AKA MIGUEL M. JIMENEZ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8695,11 +8695,11 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2028-08-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1382</v>
+        <v>662</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2030-08-03</t>
+          <t>2028-08-15</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>. CANADIAN AMERICAN LAND CO ET AL</t>
+          <t>CANADIAN AMERICAN LAND CO ET AL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>H.W. Rose / Betty Lou McQuhae aka Betty Lou Wise</t>
+          <t>Edith Dunnagan aka Edith Lena Dunnagan / Betty Lou McQuhae aka Betty Lou Wise</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>. KATIE A. DAVIS A/K/A KATIE ALBERTA DAVIS KATIE HARRIS</t>
+          <t>KATIE A. DAVIS A / K / A KATIE ALBERTA DAVIS KATIE HARRIS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>. DAVID HEROLD ET AL</t>
+          <t>DAVID HEROLD ET AL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Leroy Colbert C/O Steven Gilbert / Gertrude Colbert</t>
+          <t>Gertrude Colbert / Leroy Colbert C / O Steven Gilbert</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>. GLADYS MARSH RICHARDSON ET AL</t>
+          <t>GLADYS MARSH RICHARDSON ET AL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>. JAMES L. PRICE ET AL</t>
+          <t>JAMES L. PRICE ET AL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>. CECIL H. REYNOLDS SR. et al</t>
+          <t>CECIL H. REYNOLDS SR. et al</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>-19</v>
+        <v>-21</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11767,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>. OPAL MAE STAFFORD, A/K/A OPAL M WHITE et al</t>
+          <t>OPAL MAE STAFFORD, A / K / A OPAL M WHITE et al</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Edith Villareal Garcia / Jose Antonio Garcia</t>
+          <t>Jose Antonio Garcia / Edith Villareal Garcia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13261,7 +13261,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shawn Welch / Charles Welch</t>
+          <t>Charles Welch / Shawn Welch</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Levonia Turner / Garvey Jones</t>
+          <t>Garvey Jones / Lavonia Carlisle</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13901,7 +13901,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>. CHIKAKO MACHIDA</t>
+          <t>CHIKAKO MACHIDA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -13943,11 +13943,11 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2028-08-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1382</v>
+        <v>662</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2030-08-03</t>
+          <t>2028-08-15</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14455,7 +14455,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -14641,12 +14641,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14839,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -14897,12 +14897,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14967,7 +14967,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -15025,12 +15025,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15053,7 +15053,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>STEVE CANDA HIGH AKA STEVE CANADA HIGH SR.</t>
+          <t>STEVE CANDA HIGH AKA STEVE CANADA HIGH SR</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15153,12 +15153,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15181,7 +15181,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>. MELVIN GENE COPLIN et al</t>
+          <t>MELVIN GENE COPLIN et al</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -15223,11 +15223,11 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>2028-08-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1382</v>
+        <v>662</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2030-08-03</t>
+          <t>2028-08-15</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>. LEOLA DERRICK AKA LEOLA TURNER ET AL</t>
+          <t>LEOLA DERRICK AKA LEOLA TURNER ET AL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15409,12 +15409,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15479,11 +15479,11 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2028-08-31</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1410</v>
+        <v>694</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2030-08-31</t>
+          <t>2028-09-16</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15611,7 +15611,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15665,12 +15665,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -15793,12 +15793,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15821,7 +15821,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deondra Lynne Jackson / Hattie Mae Neal Sherman</t>
+          <t>Hattie Mae Neal Sherman / Deondra Lynne Jackson</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15995,7 +15995,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -16049,12 +16049,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16123,7 +16123,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16177,12 +16177,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16205,7 +16205,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cynthia Garner / Falisha Garner Booker</t>
+          <t>Eric Reese Garner / Chris Lynn Garner</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -16305,12 +16305,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16379,7 +16379,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16433,12 +16433,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>. EVEYLN A JONES ET AL</t>
+          <t>EVEYLN A JONES ET AL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16561,12 +16561,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>. DANIEL GONZALEZ, et al</t>
+          <t>DANIEL GONZALEZ, et al</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16689,12 +16689,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16717,7 +16717,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>George Solomon / David Solomon</t>
+          <t>Virginia Solomon / Hopie Solomon</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16845,7 +16845,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aracely Acuna / Ricardo Sosa Jr</t>
+          <t>Fred Luna Sanchez / Erasmo Leal III</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -16945,12 +16945,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>. MARY A. COOK MOSLEY ET AL</t>
+          <t>MARY A. COOK MOSLEY ET AL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -17015,11 +17015,11 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2028-08-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1382</v>
+        <v>662</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2030-08-03</t>
+          <t>2028-08-15</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Kevin Roberts / Cassandra Nunn</t>
+          <t>Raymond Roberts Jr / Gerrell Roberts</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Valenica Cruz / Daniel Valencia</t>
+          <t>Daniel Valencia / Valenica Cruz</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -17329,12 +17329,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17399,7 +17399,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -17457,12 +17457,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17585,12 +17585,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17659,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17713,12 +17713,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17787,7 +17787,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17841,12 +17841,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17915,7 +17915,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17969,12 +17969,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -18097,12 +18097,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -18167,7 +18167,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -18225,12 +18225,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -18353,12 +18353,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -18481,12 +18481,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -18551,7 +18551,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -18609,12 +18609,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -18637,7 +18637,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lillie Belle Schulze / David Curtis Schulze, individually &amp; as heir to Lillie Belle Schulze AKA</t>
+          <t>Linda King, In Rem Only / David Curtis Schulze, individually &amp; as heir to Lillie Belle Schulze AKA</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -18679,7 +18679,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -18737,12 +18737,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Albert W. Smith (2nd Address) / Della M Smith</t>
+          <t>Della M Smith / Albert W Smith</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -18865,12 +18865,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -18939,7 +18939,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -18993,12 +18993,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -19121,12 +19121,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -19249,12 +19249,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>. ROBERT COY TENNISON, JR ET AL</t>
+          <t>ROBERT COY TENNISON, JR ET AL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -19323,7 +19323,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -19377,12 +19377,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -19405,7 +19405,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>. GLADYS G. WILLIAMS</t>
+          <t>GLADYS G. WILLIAMS</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -19451,7 +19451,7 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -19505,12 +19505,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -19633,12 +19633,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -19703,7 +19703,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -19761,12 +19761,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -19835,7 +19835,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -19889,12 +19889,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -20017,12 +20017,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -20145,12 +20145,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -20215,7 +20215,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -20273,12 +20273,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -20401,12 +20401,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20475,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -20529,12 +20529,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -20657,12 +20657,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Raymond Jerry AKA Raymond J Lott / Georgia Mae Lott AKA Georgia Mae Lott Collins</t>
+          <t>Dorothy Marie Allen AKA Dorothy Marie Davis / Benjamin Levi Lott</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -20785,12 +20785,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -20913,12 +20913,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -21069,7 +21069,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bruna Hernandez Ramirez, AKA Bruna Hernandez Estorga / Annmarie Trevino</t>
+          <t>Annmarie Trevino / Bruna Hernandez Ramirez, AKA Bruna Hernandez Estorga</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -21169,12 +21169,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>. TRILAND/NORTHSTED JOINT ENTURE</t>
+          <t>TRILAND / NORTHSTED JOINT ENTURE</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -21297,12 +21297,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -21425,12 +21425,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -21453,7 +21453,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>. ROBERT SMITH ET AL</t>
+          <t>ROBERT SMITH ET AL</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -21553,12 +21553,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -21623,7 +21623,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -21681,12 +21681,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -21755,7 +21755,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -21809,12 +21809,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -21883,7 +21883,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -21937,12 +21937,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -22011,7 +22011,7 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -22065,12 +22065,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -22139,7 +22139,7 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -22193,12 +22193,12 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -22267,7 +22267,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
@@ -22321,12 +22321,12 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -22395,7 +22395,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -22449,12 +22449,12 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:37Z</t>
+          <t>2026-10-22T09:22:39Z</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Predue, Brandon, Feilder, Collins &amp; Mott, LLP / Karl W King</t>
+          <t>Predue, Brandon, Feilder, Collins &amp; Mott, LLP / Karina Andrade</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karina Andrade / Yolanda Humphrey</t>
+          <t>Linda L. Robinson / Karina Andrade</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yolanda M Humphrey / Linebarger Goggan Blair Sampson LLP</t>
+          <t>Roy Varghese Panakezham / Blair K Woodard</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alexander Freeman / Eula Webster Freeman</t>
+          <t>Predue Brandon Fielder Collins &amp; Mott LLP / Yolanda M Humphrey</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jovita Cortez Martinez / Gloria Cortez Jasso</t>
+          <t>Guadalupe Cortez / Socorro Cortez Torres</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aaron Eugene Pope / Kenyada Pope</t>
+          <t>Rosalyn Denise Pope / Tawaneka Pope</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Linbarger Goggan Blair &amp; Sampson LLP / Cinthy Pena</t>
+          <t>Mark Steven Meredith / Cinthy Pena</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11767,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rodger Dale Jablonski / Judy Jablonski AKA Judy Marie Torres</t>
+          <t>Dennis Wayne Jablonski Sr / Merlene Joyce Hinsch</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13261,7 +13261,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shawn Welch / Charles Welch</t>
+          <t>Jerri Lewis AKA Jerri Lea Lewis (3rd Address) / Jerri Lewis AKA Jerri Lea Lewis (4th Address)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13687,7 +13687,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14455,7 +14455,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -14641,12 +14641,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14839,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -14897,12 +14897,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14967,7 +14967,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -15025,12 +15025,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15153,12 +15153,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15281,12 +15281,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15409,12 +15409,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15537,12 +15537,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15611,7 +15611,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15665,12 +15665,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -15793,12 +15793,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15995,7 +15995,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -16049,12 +16049,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16123,7 +16123,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16177,12 +16177,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16205,7 +16205,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cynthia Garner / Falisha Garner Booker</t>
+          <t>Kimani Garner / Cynthia Garner</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -16305,12 +16305,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16379,7 +16379,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16433,12 +16433,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16561,12 +16561,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16689,12 +16689,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16717,7 +16717,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>George Solomon / David Solomon</t>
+          <t>Hopie Solomon / Jehu Solomon</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16845,7 +16845,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aracely Acuna / Santos Martinez</t>
+          <t>Ricardo Sosa Jr / Dolores Sosa Munoz</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -16945,12 +16945,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17073,12 +17073,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lantanya Simmons / Mable Roberts</t>
+          <t>Raymond Roberts Jr / Gerrell Roberts</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Cruz Valencia (2nd Address) (Returned Undeliverable) / Daniel Valencia (2nd Address)</t>
+          <t>Cruz Valencia (2nd Address) (Returned Undeliverable) / Valenica Cruz</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -17329,12 +17329,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17399,7 +17399,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -17457,12 +17457,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17585,12 +17585,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17659,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17713,12 +17713,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17787,7 +17787,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17841,12 +17841,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17915,7 +17915,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17969,12 +17969,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -18097,12 +18097,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18167,7 +18167,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -18225,12 +18225,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18253,7 +18253,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Donato W Benitez / Elisa Benitez</t>
+          <t>Elisa Benitez / Donato W Benitez</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -18353,12 +18353,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -18481,12 +18481,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18551,7 +18551,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -18609,12 +18609,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -18737,12 +18737,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18807,7 +18807,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -18865,12 +18865,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18939,7 +18939,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -18993,12 +18993,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -19121,12 +19121,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -19249,12 +19249,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19323,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -19377,12 +19377,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -19505,12 +19505,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -19633,12 +19633,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19703,7 +19703,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -19761,12 +19761,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19835,7 +19835,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -19889,12 +19889,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -20017,12 +20017,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -20145,12 +20145,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20215,7 +20215,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -20273,12 +20273,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -20401,12 +20401,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20475,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -20529,12 +20529,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -20657,12 +20657,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Virgie Washington AKA Virgil Lee Washington AKA Vigia Washington / Thelma Lott</t>
+          <t>Mary Ann Boldin AKA Mary An Bouldin / Sharon M. Lott AKA Sharon M Gray AKA Sharon Lott Gray</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -20785,12 +20785,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -20913,12 +20913,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -21169,12 +21169,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -21297,12 +21297,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -21425,12 +21425,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -21553,12 +21553,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21623,7 +21623,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -21681,12 +21681,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21755,7 +21755,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -21809,12 +21809,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -21883,7 +21883,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -21937,12 +21937,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22011,7 +22011,7 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -22065,12 +22065,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22139,7 +22139,7 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -22193,12 +22193,12 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22267,7 +22267,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
@@ -22321,12 +22321,12 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -22395,7 +22395,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -22449,12 +22449,12 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Predue, Brandon, Feilder, Collins &amp; Mott, LLP / Karina Andrade</t>
+          <t>Predue, Brandon, Feilder, Collins &amp; Mott, LLP / Karl W King</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>J.D. Whitehead / Clive L Sheppard</t>
+          <t>John C. Salmon (2nd Address) / J.D Whitehead (2nd Address) (Returned to Sender)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Charles F Sherwood / Sam R Casey Sr</t>
+          <t>Robert Randolph Casey Jr / Shawn Russell Casey</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sam F Elwood / Vivian Cheney</t>
+          <t>Ivo R Castlio / Sam F. Elwood (2nd Address)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Yolanda M Humphrey / Jennifer C Chiang</t>
+          <t>Blaire K Woodard / Walter Cienfuegos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lyndon M Jones / Linebarger Goggan Blair &amp; Sampson LLP</t>
+          <t>Linebarger Goggan Blair &amp; Sampson LLP / Lyndon M Jones</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11767,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dennis Wayne Jablonski Sr / Merlene Joyce Hinsch</t>
+          <t>Merlene Joyce Hinsch / Peter Victor Jablonski</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jesus Delgado Jr. AKA Jesus Delgado Sr / Juan S. Delgado AKA Juan Silva</t>
+          <t>Simon Delgado / Vicente Delgado</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13261,7 +13261,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jerri Lewis AKA Jerri Lea Lewis (3rd Address) / Jerri Lewis AKA Jerri Lea Lewis (4th Address)</t>
+          <t>Shawn Welch (3rd Address) / Heather Welch</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13687,7 +13687,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14455,7 +14455,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -14641,12 +14641,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14839,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -14897,12 +14897,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14967,7 +14967,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -15025,12 +15025,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15153,12 +15153,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15281,12 +15281,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15409,12 +15409,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15537,12 +15537,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15611,7 +15611,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15665,12 +15665,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -15793,12 +15793,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15821,7 +15821,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deondra Lynne Jackson / Hattie Mae Neal Sherman</t>
+          <t>Elaine Neal / Ida Mae Neal Sherman</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15995,7 +15995,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -16049,12 +16049,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16123,7 +16123,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16177,12 +16177,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16205,7 +16205,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kimani Garner / Cynthia Garner</t>
+          <t>Falisha Garner Booker / Tracy Garner Tyson</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -16305,12 +16305,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16379,7 +16379,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16433,12 +16433,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16561,12 +16561,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16689,12 +16689,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16717,7 +16717,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hopie Solomon / Jehu Solomon</t>
+          <t>David Solomon / George Solomon</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -16945,12 +16945,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17073,12 +17073,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Raymond Roberts Jr / Gerrell Roberts</t>
+          <t>Kevin Roberts / Cassandra Nunn</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Cruz Valencia (2nd Address) (Returned Undeliverable) / Valenica Cruz</t>
+          <t>Valenica Cruz / Daniel Valencia</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -17329,12 +17329,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17399,7 +17399,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -17457,12 +17457,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17585,12 +17585,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17659,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17713,12 +17713,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17787,7 +17787,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17841,12 +17841,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17915,7 +17915,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17969,12 +17969,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -18097,12 +18097,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18167,7 +18167,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -18225,12 +18225,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -18353,12 +18353,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -18481,12 +18481,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18551,7 +18551,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -18609,12 +18609,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -18737,12 +18737,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18807,7 +18807,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -18865,12 +18865,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18939,7 +18939,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -18993,12 +18993,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -19121,12 +19121,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19149,7 +19149,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Freddie Hatton / Gwendolyn Tatum</t>
+          <t>Larry E Spates / Gwendolyn Tatum</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -19249,12 +19249,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19323,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -19377,12 +19377,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -19505,12 +19505,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -19633,12 +19633,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Linebarger Goggan Blair &amp; Sampson / Dororothy M Davis</t>
+          <t>Dororothy M Davis / Johnny L Davis</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -19761,12 +19761,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19835,7 +19835,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -19889,12 +19889,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -20017,12 +20017,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -20145,12 +20145,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20215,7 +20215,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -20273,12 +20273,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -20401,12 +20401,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20475,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -20529,12 +20529,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -20657,12 +20657,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Mary Ann Boldin AKA Mary An Bouldin / Sharon M. Lott AKA Sharon M Gray AKA Sharon Lott Gray</t>
+          <t>Dora Mae Flowers AKA Doretta Mae Flowers / Viola Free Williams AKA Viola F Williams AKA Bonnie Free Williams</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -20785,12 +20785,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -20913,12 +20913,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -21169,12 +21169,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -21297,12 +21297,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -21425,12 +21425,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -21553,12 +21553,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21623,7 +21623,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -21681,12 +21681,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21755,7 +21755,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -21809,12 +21809,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -21883,7 +21883,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -21937,12 +21937,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22011,7 +22011,7 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -22065,12 +22065,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22139,7 +22139,7 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -22193,12 +22193,12 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22267,7 +22267,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
@@ -22321,12 +22321,12 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -22395,7 +22395,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -22449,12 +22449,12 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karl W King / Angela Kay Randermann</t>
+          <t>Predue, Brandon, Feilder, Collins &amp; Mott, LLP / Karina Andrade</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>J.D Whitehead (2nd Address) (Returned to Sender) / Frank Lamole (2nd Address) (Returned to Sender)</t>
+          <t>J.D. Whitehead / Clive L Sheppard</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Socorro Cortez Torres / Jovita Cortez Martinez</t>
+          <t>Guadalupe Cortez / Socorro Cortez Torres</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BERNARD SOLOMON / MITZI ANN PEARLMAN</t>
+          <t>George Kemp / Prisilla Kemp</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Annie Mae Green Smith / Rodney A Braxton</t>
+          <t>Mary Jo Milburn / Layne G Muegge</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mary L Garrett AKA Mary E Garrott / Fred L. Drew</t>
+          <t>Don Aubertine / Mrs. James H Dando</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Linebarger Goggan Blair &amp; Sampson LLP / Blair K Woodard</t>
+          <t>Blair K Woodard / Yolanda M Humphery</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Merlene Joyce Hinsch / Peter Victor Jablonski</t>
+          <t>Peter Victor Jablonski / Bruno Harold Dzierzanowski Jr</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jesus Delgado Jr. AKA Jesus Delgado Sr / Juan S. Delgado AKA Juan Silva</t>
+          <t>Simon Delgado / Jesus Delgado Jr. AKA Jesus Delgado Sr</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -14641,12 +14641,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14711,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -14769,12 +14769,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14897,12 +14897,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15025,12 +15025,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15153,12 +15153,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15281,12 +15281,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15409,12 +15409,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -15665,12 +15665,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15739,7 +15739,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15793,12 +15793,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15867,7 +15867,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15921,12 +15921,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Eric Reese Garner / Kimani Garner</t>
+          <t>Kimani Garner / Cynthia Garner</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16123,7 +16123,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16177,12 +16177,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16251,7 +16251,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16305,12 +16305,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16379,7 +16379,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16433,12 +16433,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16503,7 +16503,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -16561,12 +16561,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Erasmo Leal III / Fred Luna Sanchez</t>
+          <t>Aracely Acuna / Santos Martinez</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -16689,12 +16689,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16763,7 +16763,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16817,12 +16817,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -16945,12 +16945,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17275,7 +17275,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17329,12 +17329,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17457,12 +17457,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17585,12 +17585,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17659,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17713,12 +17713,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17741,7 +17741,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rev. S.E. Collins AKA Serrell E. Collins / O.B. Collins</t>
+          <t>O.B. Collins (3rd Address) / O.B. Collins (2nd Address) (Returned to Sender)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -17841,12 +17841,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17911,7 +17911,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -17969,12 +17969,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -18097,12 +18097,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -18167,7 +18167,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -18225,12 +18225,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -18353,12 +18353,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -18481,12 +18481,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -18551,7 +18551,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -18609,12 +18609,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -18683,7 +18683,7 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -18737,12 +18737,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -18865,12 +18865,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -18935,7 +18935,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -19121,12 +19121,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -19249,12 +19249,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19323,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -19377,12 +19377,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -19460,7 +19460,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -19505,12 +19505,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -19633,12 +19633,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -19703,7 +19703,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -19761,12 +19761,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -19835,7 +19835,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -19889,12 +19889,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -20017,12 +20017,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
@@ -20145,12 +20145,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -20219,7 +20219,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -20273,12 +20273,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -20347,7 +20347,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -20401,12 +20401,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sharon M. Lott AKA Sharon M Gray AKA Sharon Lott Gray / Adali Jessica Davis AKA Alice Davis</t>
+          <t>Vera Lee Love AKA Vera Lee Davis AKA Vera Davis Love / Isaac Lee Davis</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -20471,7 +20471,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -20529,12 +20529,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -20657,12 +20657,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -20731,7 +20731,7 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -20785,12 +20785,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -20855,7 +20855,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -20913,12 +20913,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -21115,7 +21115,7 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -21169,12 +21169,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -21297,12 +21297,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -21367,7 +21367,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -21425,12 +21425,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -21553,12 +21553,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -21627,7 +21627,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -21681,12 +21681,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -21755,7 +21755,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -21809,12 +21809,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -21883,7 +21883,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -21937,12 +21937,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -22011,7 +22011,7 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -22065,12 +22065,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -22139,7 +22139,7 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -22193,12 +22193,12 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
